--- a/examples/veneta/02_upd_veneta.xlsx
+++ b/examples/veneta/02_upd_veneta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,7 +438,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Наименование товара</t>
+          <t>Наименование услуги</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22500</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="6">
@@ -484,11 +484,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Canon 725</t>
+          <t>HP 58A CF258A картридж</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11400</v>
+        <v>32800</v>
       </c>
     </row>
     <row r="7">
@@ -505,11 +505,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brother TN-1075</t>
+          <t>Картридж HP CE285A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4400</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="8">
@@ -526,19 +526,460 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>HP CF410A black</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>22500</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Canon 725 картридж</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>22800</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Canon 728</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Canon 052 LBP212</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Brother TN-1075</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>8800</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Brother TN 2335 (HL-L2300)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Барабан Brother DR-2335</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Samsung MLT-D101S тонер</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>25500</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Samsung D111S тонер картридж</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Samsung MLT-D203L M3320</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Xerox 3020 106R02773</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>20400</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>25200</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Xerox WorkCentre 3215 картридж</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kyocera TK-1110 FS-1040</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kyocera TK-1170 M2040</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Epson AcuLaser C13S050709</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lexmark MS310 50F5H00</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Барабан HP CF234A</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>15600</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Тонер для заправки чёрный 1 кг</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Чип для HP CF283A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Бумага Снегурочка A4 500л</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>20</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>пачка</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Заправка картриджа HP</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Заправка цветного картриджа</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4800</v>
       </c>
     </row>
   </sheetData>
